--- a/Output Data Tables/APAT Outputs/Utilization Metrics Tables/2017/Seats_per_Departures_by_Aircraft_and_Airline_2017.xlsx
+++ b/Output Data Tables/APAT Outputs/Utilization Metrics Tables/2017/Seats_per_Departures_by_Aircraft_and_Airline_2017.xlsx
@@ -13,11 +13,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="72" uniqueCount="72">
   <si>
     <t>Row</t>
   </si>
   <si>
+    <t>E135</t>
+  </si>
+  <si>
+    <t>E140</t>
+  </si>
+  <si>
     <t>E145</t>
   </si>
   <si>
@@ -30,7 +36,19 @@
     <t>E175</t>
   </si>
   <si>
-    <t>CRJ-500</t>
+    <t>Q100</t>
+  </si>
+  <si>
+    <t>Q200</t>
+  </si>
+  <si>
+    <t>Q300</t>
+  </si>
+  <si>
+    <t>Q400</t>
+  </si>
+  <si>
+    <t>CRJ-550</t>
   </si>
   <si>
     <t>CRJ-700</t>
@@ -63,9 +81,24 @@
     <t>A321NEO</t>
   </si>
   <si>
+    <t>MD-80</t>
+  </si>
+  <si>
+    <t>MD-90</t>
+  </si>
+  <si>
     <t>B717-200</t>
   </si>
   <si>
+    <t>B737-300</t>
+  </si>
+  <si>
+    <t>B737-400</t>
+  </si>
+  <si>
+    <t>B737-500</t>
+  </si>
+  <si>
     <t>B737-700</t>
   </si>
   <si>
@@ -133,6 +166,9 @@
   </si>
   <si>
     <t>American</t>
+  </si>
+  <si>
+    <t>Avelo</t>
   </si>
   <si>
     <t>Breeze</t>
@@ -238,33 +274,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X37"/>
+  <dimension ref="A1:Y48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="true"/>
     <col min="2" max="2" width="6.85546875" customWidth="true"/>
     <col min="3" max="3" width="9.140625" customWidth="true"/>
     <col min="4" max="4" width="9.5703125" customWidth="true"/>
-    <col min="5" max="5" width="7.28515625" customWidth="true"/>
-    <col min="6" max="6" width="5.85546875" customWidth="true"/>
-    <col min="7" max="7" width="8.28515625" customWidth="true"/>
-    <col min="8" max="8" width="9.28515625" customWidth="true"/>
-    <col min="9" max="9" width="7.7109375" customWidth="true"/>
-    <col min="10" max="10" width="10.5703125" customWidth="true"/>
-    <col min="11" max="11" width="5.85546875" customWidth="true"/>
-    <col min="12" max="12" width="11.85546875" customWidth="true"/>
-    <col min="13" max="13" width="7.140625" customWidth="true"/>
-    <col min="14" max="14" width="12.42578125" customWidth="true"/>
-    <col min="15" max="15" width="9.42578125" customWidth="true"/>
-    <col min="16" max="16" width="6.42578125" customWidth="true"/>
-    <col min="17" max="17" width="6.140625" customWidth="true"/>
-    <col min="18" max="18" width="8" customWidth="true"/>
-    <col min="19" max="19" width="5.85546875" customWidth="true"/>
-    <col min="20" max="20" width="9.85546875" customWidth="true"/>
-    <col min="21" max="21" width="4.5703125" customWidth="true"/>
-    <col min="22" max="22" width="8.85546875" customWidth="true"/>
-    <col min="23" max="23" width="8.7109375" customWidth="true"/>
-    <col min="24" max="24" width="10.85546875" customWidth="true"/>
+    <col min="5" max="5" width="6.28515625" customWidth="true"/>
+    <col min="6" max="6" width="7.28515625" customWidth="true"/>
+    <col min="7" max="7" width="5.85546875" customWidth="true"/>
+    <col min="8" max="8" width="8.28515625" customWidth="true"/>
+    <col min="9" max="9" width="9.28515625" customWidth="true"/>
+    <col min="10" max="10" width="7.7109375" customWidth="true"/>
+    <col min="11" max="11" width="10.5703125" customWidth="true"/>
+    <col min="12" max="12" width="5.85546875" customWidth="true"/>
+    <col min="13" max="13" width="11.85546875" customWidth="true"/>
+    <col min="14" max="14" width="7.140625" customWidth="true"/>
+    <col min="15" max="15" width="12.42578125" customWidth="true"/>
+    <col min="16" max="16" width="9.42578125" customWidth="true"/>
+    <col min="17" max="17" width="6.42578125" customWidth="true"/>
+    <col min="18" max="18" width="6.140625" customWidth="true"/>
+    <col min="19" max="19" width="8" customWidth="true"/>
+    <col min="20" max="20" width="5.85546875" customWidth="true"/>
+    <col min="21" max="21" width="9.85546875" customWidth="true"/>
+    <col min="22" max="22" width="4.5703125" customWidth="true"/>
+    <col min="23" max="23" width="8.85546875" customWidth="true"/>
+    <col min="24" max="24" width="8.7109375" customWidth="true"/>
+    <col min="25" max="25" width="10.85546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -272,73 +309,76 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="U1" s="0" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="V1" s="0" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="W1" s="0" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="X1" s="0" t="s">
-        <v>59</v>
+        <v>70</v>
+      </c>
+      <c r="Y1" s="0" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="2">
@@ -382,13 +422,13 @@
         <v>0</v>
       </c>
       <c r="N2" s="0">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O2" s="0">
         <v>0</v>
       </c>
       <c r="P2" s="0">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="0">
         <v>0</v>
@@ -400,7 +440,7 @@
         <v>0</v>
       </c>
       <c r="T2" s="0">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="U2" s="0">
         <v>0</v>
@@ -412,7 +452,10 @@
         <v>0</v>
       </c>
       <c r="X2" s="0">
-        <v>50</v>
+        <v>0</v>
+      </c>
+      <c r="Y2" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -459,34 +502,37 @@
         <v>0</v>
       </c>
       <c r="O3" s="0">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P3" s="0">
         <v>0</v>
       </c>
       <c r="Q3" s="0">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="R3" s="0">
         <v>0</v>
       </c>
       <c r="S3" s="0">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="T3" s="0">
         <v>0</v>
       </c>
       <c r="U3" s="0">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="V3" s="0">
         <v>0</v>
       </c>
       <c r="W3" s="0">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="X3" s="0">
-        <v>50</v>
+        <v>0</v>
+      </c>
+      <c r="Y3" s="0">
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -533,13 +579,13 @@
         <v>0</v>
       </c>
       <c r="O4" s="0">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P4" s="0">
         <v>0</v>
       </c>
       <c r="Q4" s="0">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="R4" s="0">
         <v>0</v>
@@ -551,16 +597,19 @@
         <v>0</v>
       </c>
       <c r="U4" s="0">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="V4" s="0">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="W4" s="0">
         <v>0</v>
       </c>
       <c r="X4" s="0">
-        <v>70</v>
+        <v>0</v>
+      </c>
+      <c r="Y4" s="0">
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -610,31 +659,34 @@
         <v>0</v>
       </c>
       <c r="P5" s="0">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="Q5" s="0">
         <v>0</v>
       </c>
       <c r="R5" s="0">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="S5" s="0">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="T5" s="0">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="U5" s="0">
         <v>0</v>
       </c>
       <c r="V5" s="0">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="W5" s="0">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="X5" s="0">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="Y5" s="0">
+        <v>50</v>
       </c>
     </row>
     <row r="6">
@@ -705,10 +757,13 @@
         <v>0</v>
       </c>
       <c r="W6" s="0">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="X6" s="0">
         <v>0</v>
+      </c>
+      <c r="Y6" s="0">
+        <v>70</v>
       </c>
     </row>
     <row r="7">
@@ -758,31 +813,34 @@
         <v>0</v>
       </c>
       <c r="P7" s="0">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="0">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="R7" s="0">
         <v>0</v>
       </c>
       <c r="S7" s="0">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="T7" s="0">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="U7" s="0">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="V7" s="0">
         <v>0</v>
       </c>
       <c r="W7" s="0">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="X7" s="0">
-        <v>68</v>
+        <v>76</v>
+      </c>
+      <c r="Y7" s="0">
+        <v>76</v>
       </c>
     </row>
     <row r="8">
@@ -796,7 +854,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="0">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="E8" s="0">
         <v>0</v>
@@ -811,7 +869,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="0">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J8" s="0">
         <v>0</v>
@@ -847,7 +905,7 @@
         <v>0</v>
       </c>
       <c r="U8" s="0">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="V8" s="0">
         <v>0</v>
@@ -856,7 +914,10 @@
         <v>0</v>
       </c>
       <c r="X8" s="0">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="0">
+        <v>37</v>
       </c>
     </row>
     <row r="9">
@@ -903,34 +964,37 @@
         <v>0</v>
       </c>
       <c r="O9" s="0">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="P9" s="0">
         <v>0</v>
       </c>
       <c r="Q9" s="0">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="R9" s="0">
         <v>0</v>
       </c>
       <c r="S9" s="0">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="T9" s="0">
         <v>0</v>
       </c>
       <c r="U9" s="0">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="V9" s="0">
         <v>0</v>
       </c>
       <c r="W9" s="0">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="X9" s="0">
-        <v>76</v>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="0">
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -977,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="0">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P10" s="0">
         <v>0</v>
@@ -995,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="U10" s="0">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V10" s="0">
         <v>0</v>
@@ -1005,6 +1069,9 @@
       </c>
       <c r="X10" s="0">
         <v>0</v>
+      </c>
+      <c r="Y10" s="0">
+        <v>48</v>
       </c>
     </row>
     <row r="11">
@@ -1063,7 +1130,7 @@
         <v>0</v>
       </c>
       <c r="S11" s="0">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="T11" s="0">
         <v>0</v>
@@ -1079,6 +1146,9 @@
       </c>
       <c r="X11" s="0">
         <v>0</v>
+      </c>
+      <c r="Y11" s="0">
+        <v>76</v>
       </c>
     </row>
     <row r="12">
@@ -1089,19 +1159,19 @@
         <v>0</v>
       </c>
       <c r="C12" s="0">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="D12" s="0">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="E12" s="0">
         <v>0</v>
       </c>
       <c r="F12" s="0">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="G12" s="0">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H12" s="0">
         <v>0</v>
@@ -1113,13 +1183,13 @@
         <v>0</v>
       </c>
       <c r="K12" s="0">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="L12" s="0">
         <v>0</v>
       </c>
       <c r="M12" s="0">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="N12" s="0">
         <v>0</v>
@@ -1152,7 +1222,10 @@
         <v>0</v>
       </c>
       <c r="X12" s="0">
-        <v>134</v>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1163,37 +1236,37 @@
         <v>0</v>
       </c>
       <c r="C13" s="0">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="D13" s="0">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="E13" s="0">
         <v>0</v>
       </c>
       <c r="F13" s="0">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="G13" s="0">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H13" s="0">
         <v>0</v>
       </c>
       <c r="I13" s="0">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="J13" s="0">
         <v>0</v>
       </c>
       <c r="K13" s="0">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="L13" s="0">
         <v>0</v>
       </c>
       <c r="M13" s="0">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="N13" s="0">
         <v>0</v>
@@ -1205,28 +1278,31 @@
         <v>0</v>
       </c>
       <c r="Q13" s="0">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="R13" s="0">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="S13" s="0">
         <v>0</v>
       </c>
       <c r="T13" s="0">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="U13" s="0">
         <v>0</v>
       </c>
       <c r="V13" s="0">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="W13" s="0">
         <v>0</v>
       </c>
       <c r="X13" s="0">
-        <v>159</v>
+        <v>70</v>
+      </c>
+      <c r="Y13" s="0">
+        <v>68</v>
       </c>
     </row>
     <row r="14">
@@ -1240,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="0">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="E14" s="0">
         <v>0</v>
@@ -1258,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="0">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K14" s="0">
         <v>0</v>
@@ -1301,6 +1377,9 @@
       </c>
       <c r="X14" s="0">
         <v>0</v>
+      </c>
+      <c r="Y14" s="0">
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1314,28 +1393,28 @@
         <v>0</v>
       </c>
       <c r="D15" s="0">
-        <v>181</v>
+        <v>0</v>
       </c>
       <c r="E15" s="0">
         <v>0</v>
       </c>
       <c r="F15" s="0">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="G15" s="0">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="H15" s="0">
         <v>0</v>
       </c>
       <c r="I15" s="0">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="J15" s="0">
         <v>0</v>
       </c>
       <c r="K15" s="0">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="L15" s="0">
         <v>0</v>
@@ -1350,31 +1429,34 @@
         <v>0</v>
       </c>
       <c r="P15" s="0">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="Q15" s="0">
         <v>0</v>
       </c>
       <c r="R15" s="0">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="S15" s="0">
         <v>0</v>
       </c>
       <c r="T15" s="0">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="U15" s="0">
         <v>0</v>
       </c>
       <c r="V15" s="0">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="W15" s="0">
         <v>0</v>
       </c>
       <c r="X15" s="0">
-        <v>189</v>
+        <v>75</v>
+      </c>
+      <c r="Y15" s="0">
+        <v>76</v>
       </c>
     </row>
     <row r="16">
@@ -1450,6 +1532,9 @@
       <c r="X16" s="0">
         <v>0</v>
       </c>
+      <c r="Y16" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
@@ -1468,13 +1553,13 @@
         <v>0</v>
       </c>
       <c r="F17" s="0">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="G17" s="0">
         <v>0</v>
       </c>
       <c r="H17" s="0">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="I17" s="0">
         <v>0</v>
@@ -1522,7 +1607,10 @@
         <v>0</v>
       </c>
       <c r="X17" s="0">
-        <v>115</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1530,43 +1618,43 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="C18" s="0">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="D18" s="0">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="E18" s="0">
         <v>0</v>
       </c>
       <c r="F18" s="0">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="G18" s="0">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="H18" s="0">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I18" s="0">
         <v>0</v>
       </c>
       <c r="J18" s="0">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="K18" s="0">
         <v>0</v>
       </c>
       <c r="L18" s="0">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="M18" s="0">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="N18" s="0">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="O18" s="0">
         <v>0</v>
@@ -1596,7 +1684,10 @@
         <v>0</v>
       </c>
       <c r="X18" s="0">
-        <v>141</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="0">
+        <v>134</v>
       </c>
     </row>
     <row r="19">
@@ -1604,73 +1695,76 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
+        <v>0</v>
+      </c>
+      <c r="C19" s="0">
+        <v>179</v>
+      </c>
+      <c r="D19" s="0">
+        <v>150</v>
+      </c>
+      <c r="E19" s="0">
+        <v>0</v>
+      </c>
+      <c r="F19" s="0">
+        <v>0</v>
+      </c>
+      <c r="G19" s="0">
+        <v>158</v>
+      </c>
+      <c r="H19" s="0">
+        <v>180</v>
+      </c>
+      <c r="I19" s="0">
+        <v>0</v>
+      </c>
+      <c r="J19" s="0">
+        <v>150</v>
+      </c>
+      <c r="K19" s="0">
+        <v>0</v>
+      </c>
+      <c r="L19" s="0">
+        <v>180</v>
+      </c>
+      <c r="M19" s="0">
+        <v>0</v>
+      </c>
+      <c r="N19" s="0">
+        <v>150</v>
+      </c>
+      <c r="O19" s="0">
+        <v>0</v>
+      </c>
+      <c r="P19" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="0">
+        <v>0</v>
+      </c>
+      <c r="R19" s="0">
+        <v>0</v>
+      </c>
+      <c r="S19" s="0">
+        <v>0</v>
+      </c>
+      <c r="T19" s="0">
+        <v>0</v>
+      </c>
+      <c r="U19" s="0">
+        <v>0</v>
+      </c>
+      <c r="V19" s="0">
+        <v>0</v>
+      </c>
+      <c r="W19" s="0">
+        <v>0</v>
+      </c>
+      <c r="X19" s="0">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="0">
         <v>159</v>
-      </c>
-      <c r="C19" s="0">
-        <v>0</v>
-      </c>
-      <c r="D19" s="0">
-        <v>160</v>
-      </c>
-      <c r="E19" s="0">
-        <v>0</v>
-      </c>
-      <c r="F19" s="0">
-        <v>160</v>
-      </c>
-      <c r="G19" s="0">
-        <v>0</v>
-      </c>
-      <c r="H19" s="0">
-        <v>0</v>
-      </c>
-      <c r="I19" s="0">
-        <v>0</v>
-      </c>
-      <c r="J19" s="0">
-        <v>175</v>
-      </c>
-      <c r="K19" s="0">
-        <v>0</v>
-      </c>
-      <c r="L19" s="0">
-        <v>165</v>
-      </c>
-      <c r="M19" s="0">
-        <v>165</v>
-      </c>
-      <c r="N19" s="0">
-        <v>0</v>
-      </c>
-      <c r="O19" s="0">
-        <v>0</v>
-      </c>
-      <c r="P19" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="0">
-        <v>0</v>
-      </c>
-      <c r="R19" s="0">
-        <v>0</v>
-      </c>
-      <c r="S19" s="0">
-        <v>0</v>
-      </c>
-      <c r="T19" s="0">
-        <v>0</v>
-      </c>
-      <c r="U19" s="0">
-        <v>0</v>
-      </c>
-      <c r="V19" s="0">
-        <v>0</v>
-      </c>
-      <c r="W19" s="0">
-        <v>0</v>
-      </c>
-      <c r="X19" s="0">
-        <v>165</v>
       </c>
     </row>
     <row r="20">
@@ -1746,19 +1840,22 @@
       <c r="X20" s="0">
         <v>0</v>
       </c>
+      <c r="Y20" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="C21" s="0">
         <v>0</v>
       </c>
       <c r="D21" s="0">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="E21" s="0">
         <v>0</v>
@@ -1767,25 +1864,25 @@
         <v>0</v>
       </c>
       <c r="G21" s="0">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="H21" s="0">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="I21" s="0">
         <v>0</v>
       </c>
       <c r="J21" s="0">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="K21" s="0">
         <v>0</v>
       </c>
       <c r="L21" s="0">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="M21" s="0">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="N21" s="0">
         <v>0</v>
@@ -1818,7 +1915,10 @@
         <v>0</v>
       </c>
       <c r="X21" s="0">
-        <v>179</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="0">
+        <v>189</v>
       </c>
     </row>
     <row r="22">
@@ -1826,7 +1926,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="C22" s="0">
         <v>0</v>
@@ -1838,7 +1938,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="0">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G22" s="0">
         <v>0</v>
@@ -1892,7 +1992,10 @@
         <v>0</v>
       </c>
       <c r="X22" s="0">
-        <v>180</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1903,10 +2006,10 @@
         <v>0</v>
       </c>
       <c r="C23" s="0">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="D23" s="0">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="E23" s="0">
         <v>0</v>
@@ -1915,7 +2018,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="0">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="H23" s="0">
         <v>0</v>
@@ -1967,6 +2070,9 @@
       </c>
       <c r="X23" s="0">
         <v>0</v>
+      </c>
+      <c r="Y23" s="0">
+        <v>149</v>
       </c>
     </row>
     <row r="24">
@@ -1977,19 +2083,19 @@
         <v>0</v>
       </c>
       <c r="C24" s="0">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="D24" s="0">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="E24" s="0">
         <v>0</v>
       </c>
       <c r="F24" s="0">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="G24" s="0">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="H24" s="0">
         <v>0</v>
@@ -2007,7 +2113,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="0">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="N24" s="0">
         <v>0</v>
@@ -2040,7 +2146,10 @@
         <v>0</v>
       </c>
       <c r="X24" s="0">
-        <v>180</v>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="0">
+        <v>159</v>
       </c>
     </row>
     <row r="25">
@@ -2060,16 +2169,16 @@
         <v>0</v>
       </c>
       <c r="F25" s="0">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="G25" s="0">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H25" s="0">
         <v>0</v>
       </c>
       <c r="I25" s="0">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="J25" s="0">
         <v>0</v>
@@ -2081,7 +2190,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="0">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="N25" s="0">
         <v>0</v>
@@ -2114,7 +2223,10 @@
         <v>0</v>
       </c>
       <c r="X25" s="0">
-        <v>223</v>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="0">
+        <v>115</v>
       </c>
     </row>
     <row r="26">
@@ -2128,19 +2240,19 @@
         <v>0</v>
       </c>
       <c r="D26" s="0">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="E26" s="0">
         <v>0</v>
       </c>
       <c r="F26" s="0">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="G26" s="0">
         <v>0</v>
       </c>
       <c r="H26" s="0">
-        <v>258</v>
+        <v>0</v>
       </c>
       <c r="I26" s="0">
         <v>0</v>
@@ -2149,13 +2261,13 @@
         <v>0</v>
       </c>
       <c r="K26" s="0">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="L26" s="0">
         <v>0</v>
       </c>
       <c r="M26" s="0">
-        <v>202</v>
+        <v>0</v>
       </c>
       <c r="N26" s="0">
         <v>0</v>
@@ -2188,7 +2300,10 @@
         <v>0</v>
       </c>
       <c r="X26" s="0">
-        <v>215</v>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="0">
+        <v>143</v>
       </c>
     </row>
     <row r="27">
@@ -2196,7 +2311,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="C27" s="0">
         <v>0</v>
@@ -2205,10 +2320,10 @@
         <v>0</v>
       </c>
       <c r="E27" s="0">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="F27" s="0">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="G27" s="0">
         <v>0</v>
@@ -2229,7 +2344,7 @@
         <v>0</v>
       </c>
       <c r="M27" s="0">
-        <v>242</v>
+        <v>0</v>
       </c>
       <c r="N27" s="0">
         <v>0</v>
@@ -2262,7 +2377,10 @@
         <v>0</v>
       </c>
       <c r="X27" s="0">
-        <v>244</v>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="0">
+        <v>123</v>
       </c>
     </row>
     <row r="28">
@@ -2276,19 +2394,19 @@
         <v>0</v>
       </c>
       <c r="D28" s="0">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="E28" s="0">
         <v>0</v>
       </c>
       <c r="F28" s="0">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="G28" s="0">
         <v>0</v>
       </c>
       <c r="H28" s="0">
-        <v>284</v>
+        <v>0</v>
       </c>
       <c r="I28" s="0">
         <v>0</v>
@@ -2336,7 +2454,10 @@
         <v>0</v>
       </c>
       <c r="X28" s="0">
-        <v>267</v>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2344,22 +2465,22 @@
         <v>28</v>
       </c>
       <c r="B29" s="0">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="C29" s="0">
         <v>0</v>
       </c>
       <c r="D29" s="0">
-        <v>287</v>
+        <v>0</v>
       </c>
       <c r="E29" s="0">
         <v>0</v>
       </c>
       <c r="F29" s="0">
-        <v>293</v>
+        <v>0</v>
       </c>
       <c r="G29" s="0">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="H29" s="0">
         <v>0</v>
@@ -2371,16 +2492,16 @@
         <v>0</v>
       </c>
       <c r="K29" s="0">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="L29" s="0">
         <v>0</v>
       </c>
       <c r="M29" s="0">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="N29" s="0">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="O29" s="0">
         <v>0</v>
@@ -2410,7 +2531,10 @@
         <v>0</v>
       </c>
       <c r="X29" s="0">
-        <v>291</v>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="0">
+        <v>141</v>
       </c>
     </row>
     <row r="30">
@@ -2418,13 +2542,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="0">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="C30" s="0">
         <v>0</v>
       </c>
       <c r="D30" s="0">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="E30" s="0">
         <v>0</v>
@@ -2433,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="0">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="H30" s="0">
         <v>0</v>
@@ -2445,16 +2569,16 @@
         <v>0</v>
       </c>
       <c r="K30" s="0">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="L30" s="0">
         <v>0</v>
       </c>
       <c r="M30" s="0">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="N30" s="0">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="O30" s="0">
         <v>0</v>
@@ -2485,6 +2609,9 @@
       </c>
       <c r="X30" s="0">
         <v>0</v>
+      </c>
+      <c r="Y30" s="0">
+        <v>165</v>
       </c>
     </row>
     <row r="31">
@@ -2504,7 +2631,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="0">
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="G31" s="0">
         <v>0</v>
@@ -2558,7 +2685,10 @@
         <v>0</v>
       </c>
       <c r="X31" s="0">
-        <v>306</v>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2566,13 +2696,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="0">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="C32" s="0">
         <v>0</v>
       </c>
       <c r="D32" s="0">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="E32" s="0">
         <v>0</v>
@@ -2599,10 +2729,10 @@
         <v>0</v>
       </c>
       <c r="M32" s="0">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="N32" s="0">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="O32" s="0">
         <v>0</v>
@@ -2632,7 +2762,10 @@
         <v>0</v>
       </c>
       <c r="X32" s="0">
-        <v>223</v>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="0">
+        <v>179</v>
       </c>
     </row>
     <row r="33">
@@ -2640,13 +2773,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="0">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="C33" s="0">
         <v>0</v>
       </c>
       <c r="D33" s="0">
-        <v>285</v>
+        <v>0</v>
       </c>
       <c r="E33" s="0">
         <v>0</v>
@@ -2655,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="0">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H33" s="0">
         <v>0</v>
@@ -2673,7 +2806,7 @@
         <v>0</v>
       </c>
       <c r="M33" s="0">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="N33" s="0">
         <v>0</v>
@@ -2706,7 +2839,10 @@
         <v>0</v>
       </c>
       <c r="X33" s="0">
-        <v>262</v>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="0">
+        <v>180</v>
       </c>
     </row>
     <row r="34">
@@ -2782,6 +2918,9 @@
       <c r="X34" s="0">
         <v>0</v>
       </c>
+      <c r="Y34" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
@@ -2791,19 +2930,19 @@
         <v>0</v>
       </c>
       <c r="C35" s="0">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="D35" s="0">
-        <v>272</v>
+        <v>178</v>
       </c>
       <c r="E35" s="0">
         <v>0</v>
       </c>
       <c r="F35" s="0">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="G35" s="0">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="H35" s="0">
         <v>0</v>
@@ -2821,10 +2960,10 @@
         <v>0</v>
       </c>
       <c r="M35" s="0">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="N35" s="0">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="O35" s="0">
         <v>0</v>
@@ -2854,7 +2993,10 @@
         <v>0</v>
       </c>
       <c r="X35" s="0">
-        <v>290</v>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="0">
+        <v>180</v>
       </c>
     </row>
     <row r="36">
@@ -2868,7 +3010,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="0">
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="E36" s="0">
         <v>0</v>
@@ -2877,7 +3019,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="0">
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="H36" s="0">
         <v>0</v>
@@ -2895,10 +3037,10 @@
         <v>0</v>
       </c>
       <c r="M36" s="0">
-        <v>366</v>
+        <v>0</v>
       </c>
       <c r="N36" s="0">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="O36" s="0">
         <v>0</v>
@@ -2928,7 +3070,10 @@
         <v>0</v>
       </c>
       <c r="X36" s="0">
-        <v>325</v>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="0">
+        <v>223</v>
       </c>
     </row>
     <row r="37">
@@ -2936,72 +3081,922 @@
         <v>36</v>
       </c>
       <c r="B37" s="0">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="C37" s="0">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="D37" s="0">
+        <v>208</v>
+      </c>
+      <c r="E37" s="0">
+        <v>0</v>
+      </c>
+      <c r="F37" s="0">
+        <v>0</v>
+      </c>
+      <c r="G37" s="0">
+        <v>219</v>
+      </c>
+      <c r="H37" s="0">
+        <v>0</v>
+      </c>
+      <c r="I37" s="0">
+        <v>258</v>
+      </c>
+      <c r="J37" s="0">
+        <v>0</v>
+      </c>
+      <c r="K37" s="0">
+        <v>0</v>
+      </c>
+      <c r="L37" s="0">
+        <v>0</v>
+      </c>
+      <c r="M37" s="0">
+        <v>0</v>
+      </c>
+      <c r="N37" s="0">
+        <v>202</v>
+      </c>
+      <c r="O37" s="0">
+        <v>0</v>
+      </c>
+      <c r="P37" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="0">
+        <v>0</v>
+      </c>
+      <c r="R37" s="0">
+        <v>0</v>
+      </c>
+      <c r="S37" s="0">
+        <v>0</v>
+      </c>
+      <c r="T37" s="0">
+        <v>0</v>
+      </c>
+      <c r="U37" s="0">
+        <v>0</v>
+      </c>
+      <c r="V37" s="0">
+        <v>0</v>
+      </c>
+      <c r="W37" s="0">
+        <v>0</v>
+      </c>
+      <c r="X37" s="0">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="0">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="0">
+        <v>0</v>
+      </c>
+      <c r="C38" s="0">
+        <v>0</v>
+      </c>
+      <c r="D38" s="0">
+        <v>0</v>
+      </c>
+      <c r="E38" s="0">
+        <v>0</v>
+      </c>
+      <c r="F38" s="0">
+        <v>0</v>
+      </c>
+      <c r="G38" s="0">
+        <v>245</v>
+      </c>
+      <c r="H38" s="0">
+        <v>0</v>
+      </c>
+      <c r="I38" s="0">
+        <v>0</v>
+      </c>
+      <c r="J38" s="0">
+        <v>0</v>
+      </c>
+      <c r="K38" s="0">
+        <v>0</v>
+      </c>
+      <c r="L38" s="0">
+        <v>0</v>
+      </c>
+      <c r="M38" s="0">
+        <v>0</v>
+      </c>
+      <c r="N38" s="0">
+        <v>242</v>
+      </c>
+      <c r="O38" s="0">
+        <v>0</v>
+      </c>
+      <c r="P38" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="0">
+        <v>0</v>
+      </c>
+      <c r="R38" s="0">
+        <v>0</v>
+      </c>
+      <c r="S38" s="0">
+        <v>0</v>
+      </c>
+      <c r="T38" s="0">
+        <v>0</v>
+      </c>
+      <c r="U38" s="0">
+        <v>0</v>
+      </c>
+      <c r="V38" s="0">
+        <v>0</v>
+      </c>
+      <c r="W38" s="0">
+        <v>0</v>
+      </c>
+      <c r="X38" s="0">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="0">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="0">
+        <v>0</v>
+      </c>
+      <c r="C39" s="0">
+        <v>0</v>
+      </c>
+      <c r="D39" s="0">
+        <v>254</v>
+      </c>
+      <c r="E39" s="0">
+        <v>0</v>
+      </c>
+      <c r="F39" s="0">
+        <v>0</v>
+      </c>
+      <c r="G39" s="0">
+        <v>234</v>
+      </c>
+      <c r="H39" s="0">
+        <v>0</v>
+      </c>
+      <c r="I39" s="0">
+        <v>284</v>
+      </c>
+      <c r="J39" s="0">
+        <v>0</v>
+      </c>
+      <c r="K39" s="0">
+        <v>0</v>
+      </c>
+      <c r="L39" s="0">
+        <v>0</v>
+      </c>
+      <c r="M39" s="0">
+        <v>0</v>
+      </c>
+      <c r="N39" s="0">
+        <v>0</v>
+      </c>
+      <c r="O39" s="0">
+        <v>0</v>
+      </c>
+      <c r="P39" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="0">
+        <v>0</v>
+      </c>
+      <c r="R39" s="0">
+        <v>0</v>
+      </c>
+      <c r="S39" s="0">
+        <v>0</v>
+      </c>
+      <c r="T39" s="0">
+        <v>0</v>
+      </c>
+      <c r="U39" s="0">
+        <v>0</v>
+      </c>
+      <c r="V39" s="0">
+        <v>0</v>
+      </c>
+      <c r="W39" s="0">
+        <v>0</v>
+      </c>
+      <c r="X39" s="0">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="0">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="0">
+        <v>0</v>
+      </c>
+      <c r="C40" s="0">
+        <v>0</v>
+      </c>
+      <c r="D40" s="0">
+        <v>287</v>
+      </c>
+      <c r="E40" s="0">
+        <v>0</v>
+      </c>
+      <c r="F40" s="0">
+        <v>0</v>
+      </c>
+      <c r="G40" s="0">
+        <v>293</v>
+      </c>
+      <c r="H40" s="0">
+        <v>0</v>
+      </c>
+      <c r="I40" s="0">
+        <v>0</v>
+      </c>
+      <c r="J40" s="0">
+        <v>0</v>
+      </c>
+      <c r="K40" s="0">
+        <v>0</v>
+      </c>
+      <c r="L40" s="0">
+        <v>0</v>
+      </c>
+      <c r="M40" s="0">
+        <v>0</v>
+      </c>
+      <c r="N40" s="0">
+        <v>0</v>
+      </c>
+      <c r="O40" s="0">
+        <v>0</v>
+      </c>
+      <c r="P40" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="0">
+        <v>0</v>
+      </c>
+      <c r="R40" s="0">
+        <v>0</v>
+      </c>
+      <c r="S40" s="0">
+        <v>0</v>
+      </c>
+      <c r="T40" s="0">
+        <v>0</v>
+      </c>
+      <c r="U40" s="0">
+        <v>0</v>
+      </c>
+      <c r="V40" s="0">
+        <v>0</v>
+      </c>
+      <c r="W40" s="0">
+        <v>0</v>
+      </c>
+      <c r="X40" s="0">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="0">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="0">
+        <v>0</v>
+      </c>
+      <c r="C41" s="0">
+        <v>0</v>
+      </c>
+      <c r="D41" s="0">
+        <v>0</v>
+      </c>
+      <c r="E41" s="0">
+        <v>0</v>
+      </c>
+      <c r="F41" s="0">
+        <v>0</v>
+      </c>
+      <c r="G41" s="0">
+        <v>0</v>
+      </c>
+      <c r="H41" s="0">
+        <v>0</v>
+      </c>
+      <c r="I41" s="0">
+        <v>0</v>
+      </c>
+      <c r="J41" s="0">
+        <v>0</v>
+      </c>
+      <c r="K41" s="0">
+        <v>0</v>
+      </c>
+      <c r="L41" s="0">
+        <v>0</v>
+      </c>
+      <c r="M41" s="0">
+        <v>0</v>
+      </c>
+      <c r="N41" s="0">
+        <v>0</v>
+      </c>
+      <c r="O41" s="0">
+        <v>0</v>
+      </c>
+      <c r="P41" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="0">
+        <v>0</v>
+      </c>
+      <c r="R41" s="0">
+        <v>0</v>
+      </c>
+      <c r="S41" s="0">
+        <v>0</v>
+      </c>
+      <c r="T41" s="0">
+        <v>0</v>
+      </c>
+      <c r="U41" s="0">
+        <v>0</v>
+      </c>
+      <c r="V41" s="0">
+        <v>0</v>
+      </c>
+      <c r="W41" s="0">
+        <v>0</v>
+      </c>
+      <c r="X41" s="0">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="0">
+        <v>0</v>
+      </c>
+      <c r="C42" s="0">
+        <v>0</v>
+      </c>
+      <c r="D42" s="0">
+        <v>0</v>
+      </c>
+      <c r="E42" s="0">
+        <v>0</v>
+      </c>
+      <c r="F42" s="0">
+        <v>0</v>
+      </c>
+      <c r="G42" s="0">
+        <v>306</v>
+      </c>
+      <c r="H42" s="0">
+        <v>0</v>
+      </c>
+      <c r="I42" s="0">
+        <v>0</v>
+      </c>
+      <c r="J42" s="0">
+        <v>0</v>
+      </c>
+      <c r="K42" s="0">
+        <v>0</v>
+      </c>
+      <c r="L42" s="0">
+        <v>0</v>
+      </c>
+      <c r="M42" s="0">
+        <v>0</v>
+      </c>
+      <c r="N42" s="0">
+        <v>0</v>
+      </c>
+      <c r="O42" s="0">
+        <v>0</v>
+      </c>
+      <c r="P42" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="0">
+        <v>0</v>
+      </c>
+      <c r="R42" s="0">
+        <v>0</v>
+      </c>
+      <c r="S42" s="0">
+        <v>0</v>
+      </c>
+      <c r="T42" s="0">
+        <v>0</v>
+      </c>
+      <c r="U42" s="0">
+        <v>0</v>
+      </c>
+      <c r="V42" s="0">
+        <v>0</v>
+      </c>
+      <c r="W42" s="0">
+        <v>0</v>
+      </c>
+      <c r="X42" s="0">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="0">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" s="0">
+        <v>0</v>
+      </c>
+      <c r="C43" s="0">
+        <v>0</v>
+      </c>
+      <c r="D43" s="0">
+        <v>225</v>
+      </c>
+      <c r="E43" s="0">
+        <v>0</v>
+      </c>
+      <c r="F43" s="0">
+        <v>0</v>
+      </c>
+      <c r="G43" s="0">
+        <v>0</v>
+      </c>
+      <c r="H43" s="0">
+        <v>0</v>
+      </c>
+      <c r="I43" s="0">
+        <v>0</v>
+      </c>
+      <c r="J43" s="0">
+        <v>0</v>
+      </c>
+      <c r="K43" s="0">
+        <v>0</v>
+      </c>
+      <c r="L43" s="0">
+        <v>0</v>
+      </c>
+      <c r="M43" s="0">
+        <v>0</v>
+      </c>
+      <c r="N43" s="0">
+        <v>219</v>
+      </c>
+      <c r="O43" s="0">
+        <v>0</v>
+      </c>
+      <c r="P43" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="0">
+        <v>0</v>
+      </c>
+      <c r="R43" s="0">
+        <v>0</v>
+      </c>
+      <c r="S43" s="0">
+        <v>0</v>
+      </c>
+      <c r="T43" s="0">
+        <v>0</v>
+      </c>
+      <c r="U43" s="0">
+        <v>0</v>
+      </c>
+      <c r="V43" s="0">
+        <v>0</v>
+      </c>
+      <c r="W43" s="0">
+        <v>0</v>
+      </c>
+      <c r="X43" s="0">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="0">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" s="0">
+        <v>0</v>
+      </c>
+      <c r="C44" s="0">
+        <v>0</v>
+      </c>
+      <c r="D44" s="0">
+        <v>285</v>
+      </c>
+      <c r="E44" s="0">
+        <v>0</v>
+      </c>
+      <c r="F44" s="0">
+        <v>0</v>
+      </c>
+      <c r="G44" s="0">
+        <v>0</v>
+      </c>
+      <c r="H44" s="0">
+        <v>0</v>
+      </c>
+      <c r="I44" s="0">
+        <v>0</v>
+      </c>
+      <c r="J44" s="0">
+        <v>0</v>
+      </c>
+      <c r="K44" s="0">
+        <v>0</v>
+      </c>
+      <c r="L44" s="0">
+        <v>0</v>
+      </c>
+      <c r="M44" s="0">
+        <v>0</v>
+      </c>
+      <c r="N44" s="0">
+        <v>252</v>
+      </c>
+      <c r="O44" s="0">
+        <v>0</v>
+      </c>
+      <c r="P44" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="0">
+        <v>0</v>
+      </c>
+      <c r="R44" s="0">
+        <v>0</v>
+      </c>
+      <c r="S44" s="0">
+        <v>0</v>
+      </c>
+      <c r="T44" s="0">
+        <v>0</v>
+      </c>
+      <c r="U44" s="0">
+        <v>0</v>
+      </c>
+      <c r="V44" s="0">
+        <v>0</v>
+      </c>
+      <c r="W44" s="0">
+        <v>0</v>
+      </c>
+      <c r="X44" s="0">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="0">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45" s="0">
+        <v>0</v>
+      </c>
+      <c r="C45" s="0">
+        <v>0</v>
+      </c>
+      <c r="D45" s="0">
+        <v>0</v>
+      </c>
+      <c r="E45" s="0">
+        <v>0</v>
+      </c>
+      <c r="F45" s="0">
+        <v>0</v>
+      </c>
+      <c r="G45" s="0">
+        <v>0</v>
+      </c>
+      <c r="H45" s="0">
+        <v>0</v>
+      </c>
+      <c r="I45" s="0">
+        <v>0</v>
+      </c>
+      <c r="J45" s="0">
+        <v>0</v>
+      </c>
+      <c r="K45" s="0">
+        <v>0</v>
+      </c>
+      <c r="L45" s="0">
+        <v>0</v>
+      </c>
+      <c r="M45" s="0">
+        <v>0</v>
+      </c>
+      <c r="N45" s="0">
+        <v>0</v>
+      </c>
+      <c r="O45" s="0">
+        <v>0</v>
+      </c>
+      <c r="P45" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="0">
+        <v>0</v>
+      </c>
+      <c r="R45" s="0">
+        <v>0</v>
+      </c>
+      <c r="S45" s="0">
+        <v>0</v>
+      </c>
+      <c r="T45" s="0">
+        <v>0</v>
+      </c>
+      <c r="U45" s="0">
+        <v>0</v>
+      </c>
+      <c r="V45" s="0">
+        <v>0</v>
+      </c>
+      <c r="W45" s="0">
+        <v>0</v>
+      </c>
+      <c r="X45" s="0">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" s="0">
+        <v>0</v>
+      </c>
+      <c r="C46" s="0">
+        <v>0</v>
+      </c>
+      <c r="D46" s="0">
+        <v>272</v>
+      </c>
+      <c r="E46" s="0">
+        <v>0</v>
+      </c>
+      <c r="F46" s="0">
+        <v>0</v>
+      </c>
+      <c r="G46" s="0">
+        <v>291</v>
+      </c>
+      <c r="H46" s="0">
+        <v>0</v>
+      </c>
+      <c r="I46" s="0">
+        <v>0</v>
+      </c>
+      <c r="J46" s="0">
+        <v>0</v>
+      </c>
+      <c r="K46" s="0">
+        <v>0</v>
+      </c>
+      <c r="L46" s="0">
+        <v>0</v>
+      </c>
+      <c r="M46" s="0">
+        <v>0</v>
+      </c>
+      <c r="N46" s="0">
+        <v>300</v>
+      </c>
+      <c r="O46" s="0">
+        <v>0</v>
+      </c>
+      <c r="P46" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="0">
+        <v>0</v>
+      </c>
+      <c r="R46" s="0">
+        <v>0</v>
+      </c>
+      <c r="S46" s="0">
+        <v>0</v>
+      </c>
+      <c r="T46" s="0">
+        <v>0</v>
+      </c>
+      <c r="U46" s="0">
+        <v>0</v>
+      </c>
+      <c r="V46" s="0">
+        <v>0</v>
+      </c>
+      <c r="W46" s="0">
+        <v>0</v>
+      </c>
+      <c r="X46" s="0">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="0">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47" s="0">
+        <v>0</v>
+      </c>
+      <c r="C47" s="0">
+        <v>0</v>
+      </c>
+      <c r="D47" s="0">
+        <v>310</v>
+      </c>
+      <c r="E47" s="0">
+        <v>0</v>
+      </c>
+      <c r="F47" s="0">
+        <v>0</v>
+      </c>
+      <c r="G47" s="0">
+        <v>0</v>
+      </c>
+      <c r="H47" s="0">
+        <v>0</v>
+      </c>
+      <c r="I47" s="0">
+        <v>0</v>
+      </c>
+      <c r="J47" s="0">
+        <v>0</v>
+      </c>
+      <c r="K47" s="0">
+        <v>0</v>
+      </c>
+      <c r="L47" s="0">
+        <v>0</v>
+      </c>
+      <c r="M47" s="0">
+        <v>0</v>
+      </c>
+      <c r="N47" s="0">
+        <v>366</v>
+      </c>
+      <c r="O47" s="0">
+        <v>0</v>
+      </c>
+      <c r="P47" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="0">
+        <v>0</v>
+      </c>
+      <c r="R47" s="0">
+        <v>0</v>
+      </c>
+      <c r="S47" s="0">
+        <v>0</v>
+      </c>
+      <c r="T47" s="0">
+        <v>0</v>
+      </c>
+      <c r="U47" s="0">
+        <v>0</v>
+      </c>
+      <c r="V47" s="0">
+        <v>0</v>
+      </c>
+      <c r="W47" s="0">
+        <v>0</v>
+      </c>
+      <c r="X47" s="0">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="0">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48" s="0">
+        <v>163</v>
+      </c>
+      <c r="C48" s="0">
+        <v>168</v>
+      </c>
+      <c r="D48" s="0">
+        <v>163</v>
+      </c>
+      <c r="E48" s="0">
+        <v>168</v>
+      </c>
+      <c r="F48" s="0">
+        <v>0</v>
+      </c>
+      <c r="G48" s="0">
+        <v>161</v>
+      </c>
+      <c r="H48" s="0">
+        <v>184</v>
+      </c>
+      <c r="I48" s="0">
         <v>165</v>
       </c>
-      <c r="E37" s="0">
-        <v>0</v>
-      </c>
-      <c r="F37" s="0">
-        <v>164</v>
-      </c>
-      <c r="G37" s="0">
-        <v>184</v>
-      </c>
-      <c r="H37" s="0">
-        <v>165</v>
-      </c>
-      <c r="I37" s="0">
+      <c r="J48" s="0">
         <v>138</v>
       </c>
-      <c r="J37" s="0">
-        <v>150</v>
-      </c>
-      <c r="K37" s="0">
+      <c r="K48" s="0">
+        <v>149</v>
+      </c>
+      <c r="L48" s="0">
         <v>179</v>
       </c>
-      <c r="L37" s="0">
+      <c r="M48" s="0">
         <v>155</v>
       </c>
-      <c r="M37" s="0">
+      <c r="N48" s="0">
         <v>171</v>
       </c>
-      <c r="N37" s="0">
-        <v>50</v>
-      </c>
-      <c r="O37" s="0">
+      <c r="O48" s="0">
+        <v>45</v>
+      </c>
+      <c r="P48" s="0">
         <v>65</v>
       </c>
-      <c r="P37" s="0">
-        <v>60</v>
-      </c>
-      <c r="Q37" s="0">
+      <c r="Q48" s="0">
+        <v>59</v>
+      </c>
+      <c r="R48" s="0">
         <v>71</v>
       </c>
-      <c r="R37" s="0">
+      <c r="S48" s="0">
         <v>76</v>
       </c>
-      <c r="S37" s="0">
+      <c r="T48" s="0">
         <v>76</v>
       </c>
-      <c r="T37" s="0">
-        <v>50</v>
-      </c>
-      <c r="U37" s="0">
+      <c r="U48" s="0">
+        <v>47</v>
+      </c>
+      <c r="V48" s="0">
         <v>67</v>
       </c>
-      <c r="V37" s="0">
+      <c r="W48" s="0">
         <v>74</v>
       </c>
-      <c r="W37" s="0">
+      <c r="X48" s="0">
         <v>62</v>
       </c>
-      <c r="X37" s="0">
+      <c r="Y48" s="0">
         <v>131</v>
       </c>
     </row>

--- a/Output Data Tables/APAT Outputs/Utilization Metrics Tables/2017/Seats_per_Departures_by_Aircraft_and_Airline_2017.xlsx
+++ b/Output Data Tables/APAT Outputs/Utilization Metrics Tables/2017/Seats_per_Departures_by_Aircraft_and_Airline_2017.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="72" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="76" uniqueCount="76">
   <si>
     <t>Row</t>
   </si>
@@ -226,6 +226,18 @@
   </si>
   <si>
     <t>SkyWest</t>
+  </si>
+  <si>
+    <t>FSC</t>
+  </si>
+  <si>
+    <t>Hybrid</t>
+  </si>
+  <si>
+    <t>ULCC</t>
+  </si>
+  <si>
+    <t>Regional</t>
   </si>
   <si>
     <t>All Airlines</t>
@@ -274,7 +286,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y48"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="true"/>
@@ -301,7 +313,11 @@
     <col min="22" max="22" width="4.5703125" customWidth="true"/>
     <col min="23" max="23" width="8.85546875" customWidth="true"/>
     <col min="24" max="24" width="8.7109375" customWidth="true"/>
-    <col min="25" max="25" width="10.85546875" customWidth="true"/>
+    <col min="25" max="25" width="4.28515625" customWidth="true"/>
+    <col min="26" max="26" width="7" customWidth="true"/>
+    <col min="27" max="27" width="5.5703125" customWidth="true"/>
+    <col min="28" max="28" width="8.85546875" customWidth="true"/>
+    <col min="29" max="29" width="10.85546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -380,6 +396,18 @@
       <c r="Y1" s="0" t="s">
         <v>71</v>
       </c>
+      <c r="Z1" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA1" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB1" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC1" s="0" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
@@ -457,6 +485,18 @@
       <c r="Y2" s="0">
         <v>0</v>
       </c>
+      <c r="Z2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
@@ -532,6 +572,18 @@
         <v>0</v>
       </c>
       <c r="Y3" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="0">
+        <v>44</v>
+      </c>
+      <c r="AC3" s="0">
         <v>44</v>
       </c>
     </row>
@@ -609,6 +661,18 @@
         <v>0</v>
       </c>
       <c r="Y4" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="0">
+        <v>50</v>
+      </c>
+      <c r="AC4" s="0">
         <v>50</v>
       </c>
     </row>
@@ -686,6 +750,18 @@
         <v>50</v>
       </c>
       <c r="Y5" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="0">
+        <v>50</v>
+      </c>
+      <c r="AC5" s="0">
         <v>50</v>
       </c>
     </row>
@@ -763,6 +839,18 @@
         <v>0</v>
       </c>
       <c r="Y6" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="0">
+        <v>70</v>
+      </c>
+      <c r="AC6" s="0">
         <v>70</v>
       </c>
     </row>
@@ -840,6 +928,18 @@
         <v>76</v>
       </c>
       <c r="Y7" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="0">
+        <v>76</v>
+      </c>
+      <c r="AC7" s="0">
         <v>76</v>
       </c>
     </row>
@@ -917,6 +1017,18 @@
         <v>0</v>
       </c>
       <c r="Y8" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="0">
+        <v>37</v>
+      </c>
+      <c r="AC8" s="0">
         <v>37</v>
       </c>
     </row>
@@ -994,6 +1106,18 @@
         <v>0</v>
       </c>
       <c r="Y9" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="0">
+        <v>37</v>
+      </c>
+      <c r="AC9" s="0">
         <v>37</v>
       </c>
     </row>
@@ -1071,6 +1195,18 @@
         <v>0</v>
       </c>
       <c r="Y10" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="0">
+        <v>48</v>
+      </c>
+      <c r="AC10" s="0">
         <v>48</v>
       </c>
     </row>
@@ -1148,6 +1284,18 @@
         <v>0</v>
       </c>
       <c r="Y11" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="0">
+        <v>76</v>
+      </c>
+      <c r="AC11" s="0">
         <v>76</v>
       </c>
     </row>
@@ -1227,6 +1375,18 @@
       <c r="Y12" s="0">
         <v>0</v>
       </c>
+      <c r="Z12" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
@@ -1302,6 +1462,18 @@
         <v>70</v>
       </c>
       <c r="Y13" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="0">
+        <v>68</v>
+      </c>
+      <c r="AC13" s="0">
         <v>68</v>
       </c>
     </row>
@@ -1379,6 +1551,18 @@
         <v>0</v>
       </c>
       <c r="Y14" s="0">
+        <v>99</v>
+      </c>
+      <c r="Z14" s="0">
+        <v>100</v>
+      </c>
+      <c r="AA14" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="0">
         <v>100</v>
       </c>
     </row>
@@ -1456,6 +1640,18 @@
         <v>75</v>
       </c>
       <c r="Y15" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="0">
+        <v>76</v>
+      </c>
+      <c r="AC15" s="0">
         <v>76</v>
       </c>
     </row>
@@ -1535,6 +1731,18 @@
       <c r="Y16" s="0">
         <v>0</v>
       </c>
+      <c r="Z16" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
@@ -1612,6 +1820,18 @@
       <c r="Y17" s="0">
         <v>0</v>
       </c>
+      <c r="Z17" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
@@ -1687,6 +1907,18 @@
         <v>0</v>
       </c>
       <c r="Y18" s="0">
+        <v>129</v>
+      </c>
+      <c r="Z18" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="0">
+        <v>150</v>
+      </c>
+      <c r="AB18" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="0">
         <v>134</v>
       </c>
     </row>
@@ -1764,6 +1996,18 @@
         <v>0</v>
       </c>
       <c r="Y19" s="0">
+        <v>153</v>
+      </c>
+      <c r="Z19" s="0">
+        <v>150</v>
+      </c>
+      <c r="AA19" s="0">
+        <v>180</v>
+      </c>
+      <c r="AB19" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="0">
         <v>159</v>
       </c>
     </row>
@@ -1843,6 +2087,18 @@
       <c r="Y20" s="0">
         <v>0</v>
       </c>
+      <c r="Z20" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
@@ -1918,6 +2174,18 @@
         <v>0</v>
       </c>
       <c r="Y21" s="0">
+        <v>182</v>
+      </c>
+      <c r="Z21" s="0">
+        <v>184</v>
+      </c>
+      <c r="AA21" s="0">
+        <v>229</v>
+      </c>
+      <c r="AB21" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="0">
         <v>189</v>
       </c>
     </row>
@@ -1997,6 +2265,18 @@
       <c r="Y22" s="0">
         <v>0</v>
       </c>
+      <c r="Z22" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
@@ -2072,6 +2352,18 @@
         <v>0</v>
       </c>
       <c r="Y23" s="0">
+        <v>147</v>
+      </c>
+      <c r="Z23" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="0">
+        <v>166</v>
+      </c>
+      <c r="AB23" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="0">
         <v>149</v>
       </c>
     </row>
@@ -2151,6 +2443,18 @@
       <c r="Y24" s="0">
         <v>159</v>
       </c>
+      <c r="Z24" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="0">
+        <v>159</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
@@ -2226,6 +2530,18 @@
         <v>0</v>
       </c>
       <c r="Y25" s="0">
+        <v>110</v>
+      </c>
+      <c r="Z25" s="0">
+        <v>128</v>
+      </c>
+      <c r="AA25" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="0">
         <v>115</v>
       </c>
     </row>
@@ -2303,6 +2619,18 @@
         <v>0</v>
       </c>
       <c r="Y26" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="0">
+        <v>143</v>
+      </c>
+      <c r="AA26" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="0">
         <v>143</v>
       </c>
     </row>
@@ -2380,6 +2708,18 @@
         <v>0</v>
       </c>
       <c r="Y27" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="0">
+        <v>113</v>
+      </c>
+      <c r="AA27" s="0">
+        <v>168</v>
+      </c>
+      <c r="AB27" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="0">
         <v>123</v>
       </c>
     </row>
@@ -2459,6 +2799,18 @@
       <c r="Y28" s="0">
         <v>0</v>
       </c>
+      <c r="Z28" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
@@ -2534,6 +2886,18 @@
         <v>0</v>
       </c>
       <c r="Y29" s="0">
+        <v>122</v>
+      </c>
+      <c r="Z29" s="0">
+        <v>143</v>
+      </c>
+      <c r="AA29" s="0">
+        <v>129</v>
+      </c>
+      <c r="AB29" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="0">
         <v>141</v>
       </c>
     </row>
@@ -2611,6 +2975,18 @@
         <v>0</v>
       </c>
       <c r="Y30" s="0">
+        <v>161</v>
+      </c>
+      <c r="Z30" s="0">
+        <v>172</v>
+      </c>
+      <c r="AA30" s="0">
+        <v>165</v>
+      </c>
+      <c r="AB30" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="0">
         <v>165</v>
       </c>
     </row>
@@ -2690,6 +3066,18 @@
       <c r="Y31" s="0">
         <v>0</v>
       </c>
+      <c r="Z31" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
@@ -2767,6 +3155,18 @@
       <c r="Y32" s="0">
         <v>179</v>
       </c>
+      <c r="Z32" s="0">
+        <v>179</v>
+      </c>
+      <c r="AA32" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="0">
+        <v>179</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
@@ -2844,6 +3244,18 @@
       <c r="Y33" s="0">
         <v>180</v>
       </c>
+      <c r="Z33" s="0">
+        <v>179</v>
+      </c>
+      <c r="AA33" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="0">
+        <v>180</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
@@ -2921,6 +3333,18 @@
       <c r="Y34" s="0">
         <v>0</v>
       </c>
+      <c r="Z34" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
@@ -2996,6 +3420,18 @@
         <v>0</v>
       </c>
       <c r="Y35" s="0">
+        <v>179</v>
+      </c>
+      <c r="Z35" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="0">
+        <v>215</v>
+      </c>
+      <c r="AB35" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="0">
         <v>180</v>
       </c>
     </row>
@@ -3075,6 +3511,18 @@
       <c r="Y36" s="0">
         <v>223</v>
       </c>
+      <c r="Z36" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="0">
+        <v>223</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
@@ -3150,6 +3598,18 @@
         <v>0</v>
       </c>
       <c r="Y37" s="0">
+        <v>212</v>
+      </c>
+      <c r="Z37" s="0">
+        <v>258</v>
+      </c>
+      <c r="AA37" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="0">
         <v>215</v>
       </c>
     </row>
@@ -3229,6 +3689,18 @@
       <c r="Y38" s="0">
         <v>244</v>
       </c>
+      <c r="Z38" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="0">
+        <v>244</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
@@ -3304,6 +3776,18 @@
         <v>0</v>
       </c>
       <c r="Y39" s="0">
+        <v>247</v>
+      </c>
+      <c r="Z39" s="0">
+        <v>284</v>
+      </c>
+      <c r="AA39" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="0">
         <v>267</v>
       </c>
     </row>
@@ -3383,6 +3867,18 @@
       <c r="Y40" s="0">
         <v>291</v>
       </c>
+      <c r="Z40" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB40" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="0">
+        <v>291</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
@@ -3460,6 +3956,18 @@
       <c r="Y41" s="0">
         <v>0</v>
       </c>
+      <c r="Z41" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
@@ -3537,6 +4045,18 @@
       <c r="Y42" s="0">
         <v>306</v>
       </c>
+      <c r="Z42" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="0">
+        <v>306</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
@@ -3614,6 +4134,18 @@
       <c r="Y43" s="0">
         <v>223</v>
       </c>
+      <c r="Z43" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="0">
+        <v>223</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
@@ -3691,6 +4223,18 @@
       <c r="Y44" s="0">
         <v>262</v>
       </c>
+      <c r="Z44" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="0">
+        <v>262</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
@@ -3768,6 +4312,18 @@
       <c r="Y45" s="0">
         <v>0</v>
       </c>
+      <c r="Z45" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
@@ -3845,6 +4401,18 @@
       <c r="Y46" s="0">
         <v>290</v>
       </c>
+      <c r="Z46" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB46" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="0">
+        <v>290</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
@@ -3922,6 +4490,18 @@
       <c r="Y47" s="0">
         <v>325</v>
       </c>
+      <c r="Z47" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="0">
+        <v>325</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
@@ -3997,6 +4577,18 @@
         <v>62</v>
       </c>
       <c r="Y48" s="0">
+        <v>164</v>
+      </c>
+      <c r="Z48" s="0">
+        <v>149</v>
+      </c>
+      <c r="AA48" s="0">
+        <v>176</v>
+      </c>
+      <c r="AB48" s="0">
+        <v>66</v>
+      </c>
+      <c r="AC48" s="0">
         <v>131</v>
       </c>
     </row>
